--- a/sheets/대금율보/검수/상령산.xlsx
+++ b/sheets/대금율보/검수/상령산.xlsx
@@ -5243,32 +5243,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="18.03" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="18.03" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="18.03" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="114.29" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="127.9" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="127.9" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="22"/>
@@ -5415,7 +5415,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="127.9" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="127.9" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="127.9" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -5634,7 +5634,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="127.9" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="U8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="127.9" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="127.9" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="U10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="127.9" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="127.9" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="127.9" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="U13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="127.9" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="U14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="127.9" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
       <c r="T15" s="21"/>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="127.9" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="U16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="127.9" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="127.9" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
       </c>
       <c r="U18" s="22"/>
     </row>
-    <row r="19">
+    <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="114.29" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="127.9" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="127.9" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="22"/>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="U22" s="22"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="127.9" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="127.9" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="22"/>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="U24" s="22"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="127.9" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -6551,7 +6551,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="127.9" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -6574,7 +6574,7 @@
       <c r="T26" s="21"/>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="127.9" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="22"/>
@@ -6597,7 +6597,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="22"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="127.9" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="22"/>
@@ -6620,7 +6620,7 @@
       <c r="T28" s="21"/>
       <c r="U28" s="22"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="127.9" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="127.9" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="22"/>
@@ -6670,7 +6670,7 @@
       <c r="T30" s="21"/>
       <c r="U30" s="22"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="127.9" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="22"/>
@@ -6693,7 +6693,7 @@
       <c r="T31" s="21"/>
       <c r="U31" s="22"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="127.9" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="22"/>
@@ -6716,7 +6716,7 @@
       <c r="T32" s="21"/>
       <c r="U32" s="22"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="127.9" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -6739,7 +6739,7 @@
       <c r="T33" s="21"/>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="127.9" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="22"/>
@@ -6762,7 +6762,7 @@
       <c r="T34" s="21"/>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="127.9" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="22"/>
@@ -6785,7 +6785,7 @@
       <c r="T35" s="21"/>
       <c r="U35" s="22"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="127.9" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="22"/>
@@ -6815,7 +6815,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="35"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="18" max="16383" man="1"/>
   </rowBreaks>

--- a/sheets/대금율보/검수/상령산.xlsx
+++ b/sheets/대금율보/검수/상령산.xlsx
@@ -5358,7 +5358,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢○
+          <t xml:space="preserve">潢
 –И
 ㅣ南林·</t>
         </is>
@@ -5427,7 +5427,7 @@
       <c r="C5" s="22"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢○</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="E5" s="22"/>
@@ -5638,7 +5638,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢○</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="C8" s="22"/>
@@ -6085,7 +6085,7 @@
       <c r="Q14" s="22"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢○</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="S14" s="22"/>
@@ -6276,7 +6276,7 @@
       <c r="M17" s="22"/>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃○
+          <t xml:space="preserve">黃
 –
 –И</t>
         </is>
@@ -6284,7 +6284,7 @@
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢○</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="Q17" s="22"/>
